--- a/data/website-data.xlsx
+++ b/data/website-data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Website\Shiraz_Khurana_Website_Unified_Data\Shiraz_Khurana_Website_Unified_Data\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Website\Shiraz_Khurana_Website_Unified_Data\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02C7298D-8F1F-42C8-87C8-C1DFBEB66655}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D285E024-D50F-4D43-8002-A25F30AF1698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Publications" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="177">
   <si>
     <t>year</t>
   </si>
@@ -332,15 +332,6 @@
     <t>assets/downloads/other/DBMS_Navathe.pdf</t>
   </si>
   <si>
-    <t>Digital_Image_Processing_4th_Edition</t>
-  </si>
-  <si>
-    <t>Reference book for ML</t>
-  </si>
-  <si>
-    <t>assets/downloads/other/Digital_Image_Processing_4th_Edition.pdf</t>
-  </si>
-  <si>
     <t>level</t>
   </si>
   <si>
@@ -547,6 +538,24 @@
   <si>
     <t>assets\workshops\IA Online Training Certificate.pdf</t>
   </si>
+  <si>
+    <t>DBMS Theory Syllabus</t>
+  </si>
+  <si>
+    <t>Theory Syllabus</t>
+  </si>
+  <si>
+    <t>assets/downloads/other/DBMS_Theory_Syllabus.pdf</t>
+  </si>
+  <si>
+    <t>assets/downloads/other/DBMS_Lab_Syllabus.pdf</t>
+  </si>
+  <si>
+    <t>Lab Syllabus</t>
+  </si>
+  <si>
+    <t>DBMS Lab Syllabus</t>
+  </si>
 </sst>
 </file>
 
@@ -643,7 +652,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="DownloadsTable" displayName="DownloadsTable" ref="A1:J200">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="DownloadsTable" displayName="DownloadsTable" ref="A1:J199">
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="category"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="title"/>
@@ -10687,7 +10696,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J500"/>
+  <dimension ref="A1:J499"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -10781,41 +10790,53 @@
         <v>101</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="27.6">
+    <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
         <v>94</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>102</v>
+        <v>171</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2" t="s">
-        <v>103</v>
+        <v>172</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>98</v>
       </c>
       <c r="I4" s="2"/>
       <c r="J4" s="2" t="s">
-        <v>104</v>
+        <v>173</v>
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
+      <c r="A5" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>96</v>
+      </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
+      <c r="G5" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>98</v>
+      </c>
       <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
+      <c r="J5" s="2" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2"/>
@@ -16745,24 +16766,12 @@
       <c r="I499" s="2"/>
       <c r="J499" s="2"/>
     </row>
-    <row r="500" spans="1:10">
-      <c r="A500" s="2"/>
-      <c r="B500" s="2"/>
-      <c r="C500" s="2"/>
-      <c r="D500" s="2"/>
-      <c r="E500" s="2"/>
-      <c r="F500" s="2"/>
-      <c r="G500" s="2"/>
-      <c r="H500" s="2"/>
-      <c r="I500" s="2"/>
-      <c r="J500" s="2"/>
-    </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" sqref="A2:A500" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" sqref="A2:A499" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"question-paper,notes,presentation,other"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="H2:H500" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" sqref="H2:H499" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"PDF,PPTX,DOCX,XLSX,ZIP,Image,Other"</formula1>
     </dataValidation>
   </dataValidations>
@@ -16792,78 +16801,78 @@
   <sheetData>
     <row r="1" spans="1:14" ht="24" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>113</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>14</v>
       </c>
       <c r="M1" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="27.6">
+      <c r="A2" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" ht="27.6">
-      <c r="A2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>116</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>119</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>17</v>
       </c>
       <c r="F2" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>121</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>124</v>
       </c>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
@@ -16872,34 +16881,34 @@
     </row>
     <row r="3" spans="1:14" ht="41.4">
       <c r="A3" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>17</v>
       </c>
       <c r="F3" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>121</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>124</v>
       </c>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
@@ -16908,34 +16917,34 @@
     </row>
     <row r="4" spans="1:14" ht="27.6">
       <c r="A4" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>17</v>
       </c>
       <c r="F4" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>121</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>124</v>
       </c>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
@@ -16944,34 +16953,34 @@
     </row>
     <row r="5" spans="1:14" ht="27.6">
       <c r="A5" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>17</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
@@ -16980,34 +16989,34 @@
     </row>
     <row r="6" spans="1:14" ht="27.6">
       <c r="A6" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>17</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
@@ -24951,7 +24960,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="24" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -24963,33 +24972,33 @@
         <v>90</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>140</v>
-      </c>
     </row>
     <row r="2" spans="1:9" ht="27.6">
       <c r="A2" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
@@ -24999,16 +25008,16 @@
     </row>
     <row r="3" spans="1:9" ht="41.4">
       <c r="A3" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
@@ -25018,16 +25027,16 @@
     </row>
     <row r="4" spans="1:9" ht="27.6">
       <c r="A4" s="2" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
@@ -30528,16 +30537,16 @@
         <v>90</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>93</v>
@@ -30545,11 +30554,11 @@
     </row>
     <row r="2" spans="1:9" ht="27.6">
       <c r="A2" s="2" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
@@ -30560,40 +30569,40 @@
     </row>
     <row r="3" spans="1:9" ht="27.6">
       <c r="A3" s="2" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B3" s="2">
         <v>2025</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="G3" s="3">
         <v>45974</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="27.6">
       <c r="A4" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -30604,11 +30613,11 @@
     </row>
     <row r="5" spans="1:9" ht="27.6">
       <c r="A5" s="2" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
@@ -30619,11 +30628,11 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -30634,11 +30643,11 @@
     </row>
     <row r="7" spans="1:9" ht="27.6">
       <c r="A7" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -30649,11 +30658,11 @@
     </row>
     <row r="8" spans="1:9" ht="27.6">
       <c r="A8" s="2" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -30664,11 +30673,11 @@
     </row>
     <row r="9" spans="1:9" ht="27.6">
       <c r="A9" s="2" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
